--- a/data/trans_dic/P15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,95</t>
+          <t>5,02; 9,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,87</t>
+          <t>5,08; 10,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,58</t>
+          <t>3,26; 7,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,3</t>
+          <t>3,03; 6,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,17</t>
+          <t>3,24; 9,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,18</t>
+          <t>3,05; 9,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,96</t>
+          <t>3,48; 8,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,95</t>
+          <t>3,72; 7,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,44</t>
+          <t>4,74; 8,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,21</t>
+          <t>5,15; 9,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,5</t>
+          <t>3,92; 7,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,3</t>
+          <t>3,77; 6,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,25</t>
+          <t>4,49; 10,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,83</t>
+          <t>5,35; 10,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,02</t>
+          <t>2,52; 6,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,43</t>
+          <t>3,46; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,29</t>
+          <t>1,53; 5,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,35</t>
+          <t>5,27; 11,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,13</t>
+          <t>3,75; 9,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,16</t>
+          <t>4,39; 8,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,09</t>
+          <t>3,56; 7,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,88</t>
+          <t>6,06; 10,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,05</t>
+          <t>3,6; 7,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,47</t>
+          <t>4,35; 7,56</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,63</t>
+          <t>6,76; 11,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 12,13</t>
+          <t>7,21; 12,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 8,56</t>
+          <t>3,99; 8,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,95</t>
+          <t>1,77; 8,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,42</t>
+          <t>1,05; 6,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,49</t>
+          <t>3,55; 9,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,69</t>
+          <t>3,13; 10,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,89</t>
+          <t>4,67; 10,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,66</t>
+          <t>5,63; 9,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,92</t>
+          <t>6,78; 10,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,98</t>
+          <t>4,18; 7,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,46</t>
+          <t>2,38; 8,06</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,39</t>
+          <t>5,33; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,0</t>
+          <t>6,85; 10,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,42</t>
+          <t>3,94; 6,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,29</t>
+          <t>4,97; 8,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,33</t>
+          <t>4,37; 8,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,41</t>
+          <t>4,76; 8,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,32</t>
+          <t>3,38; 6,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,21</t>
+          <t>2,6; 6,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,73</t>
+          <t>5,45; 7,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,93</t>
+          <t>6,39; 8,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 5,97</t>
+          <t>4,07; 5,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,1</t>
+          <t>4,05; 7,06</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,95</t>
+          <t>3,69; 8,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,39</t>
+          <t>5,69; 10,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,89</t>
+          <t>4,91; 8,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,44</t>
+          <t>5,73; 11,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,97</t>
+          <t>4,63; 8,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 9,92</t>
+          <t>6,11; 9,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,3</t>
+          <t>3,94; 7,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,11</t>
+          <t>4,61; 8,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,86</t>
+          <t>4,74; 7,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,19</t>
+          <t>6,23; 9,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,36</t>
+          <t>4,78; 7,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,54</t>
+          <t>5,45; 8,5</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,45</t>
+          <t>6,78; 13,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 14,08</t>
+          <t>7,09; 14,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 14,99</t>
+          <t>7,06; 14,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,13</t>
+          <t>1,78; 13,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,36</t>
+          <t>3,9; 6,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,17</t>
+          <t>6,7; 10,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,25</t>
+          <t>4,18; 7,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,09</t>
+          <t>4,69; 7,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,16</t>
+          <t>4,89; 7,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 9,99</t>
+          <t>7,19; 10,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,19</t>
+          <t>5,25; 7,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,9</t>
+          <t>4,54; 7,69</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,33</t>
+          <t>6,52; 8,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,44</t>
+          <t>7,45; 9,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,75</t>
+          <t>5,14; 6,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,95</t>
+          <t>4,66; 6,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,96</t>
+          <t>4,47; 5,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,21</t>
+          <t>6,39; 8,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 6,24</t>
+          <t>4,67; 6,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,67</t>
+          <t>4,69; 6,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,9</t>
+          <t>5,68; 6,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,52</t>
+          <t>7,2; 8,55</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,21</t>
+          <t>5,11; 6,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,51</t>
+          <t>5,03; 6,55</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23843; 47119</t>
+          <t>23796; 46588</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22497; 47538</t>
+          <t>22208; 47494</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13496; 32507</t>
+          <t>13977; 32795</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15609; 36869</t>
+          <t>15308; 34218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9368; 25056</t>
+          <t>9945; 27953</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9608; 28862</t>
+          <t>9595; 28982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13080; 31091</t>
+          <t>12075; 31052</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17353; 31084</t>
+          <t>16625; 31524</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37093; 65840</t>
+          <t>36958; 64556</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36761; 69224</t>
+          <t>38699; 69358</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30217; 58247</t>
+          <t>30462; 58220</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36163; 60007</t>
+          <t>35877; 59482</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16540; 37629</t>
+          <t>16463; 38035</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23109; 45361</t>
+          <t>22398; 44102</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10327; 26488</t>
+          <t>9524; 26010</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15601; 38114</t>
+          <t>15650; 37578</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5867; 19654</t>
+          <t>5699; 21507</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16975; 38374</t>
+          <t>17824; 38741</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13393; 34000</t>
+          <t>13976; 35178</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16562; 31219</t>
+          <t>16784; 31157</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26927; 52394</t>
+          <t>26292; 52608</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44568; 74806</t>
+          <t>45856; 76549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27801; 52874</t>
+          <t>26953; 53097</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36821; 62354</t>
+          <t>36309; 63142</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36365; 63071</t>
+          <t>36645; 63541</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44787; 76327</t>
+          <t>45351; 77805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21506; 44672</t>
+          <t>20828; 42550</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11686; 59823</t>
+          <t>11800; 58436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1792; 10775</t>
+          <t>1762; 10461</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9032; 24692</t>
+          <t>9239; 25397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4657; 17751</t>
+          <t>5203; 17919</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7666; 18175</t>
+          <t>7791; 17617</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39924; 68587</t>
+          <t>39994; 68250</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61117; 97122</t>
+          <t>60317; 95421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29733; 54894</t>
+          <t>28773; 54294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17399; 70629</t>
+          <t>19841; 67314</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68360; 103921</t>
+          <t>65963; 102641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>77820; 115875</t>
+          <t>79419; 117409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45533; 73762</t>
+          <t>45342; 75025</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50973; 85812</t>
+          <t>51470; 83262</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32371; 59473</t>
+          <t>31230; 58322</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36752; 64466</t>
+          <t>36470; 65004</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27862; 52227</t>
+          <t>27892; 53319</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26393; 70531</t>
+          <t>25466; 67826</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>106409; 150905</t>
+          <t>106400; 150832</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124493; 172013</t>
+          <t>122997; 169692</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78386; 118033</t>
+          <t>80397; 118147</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82058; 142881</t>
+          <t>81569; 142206</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13484; 31382</t>
+          <t>12942; 30934</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28438; 53045</t>
+          <t>29056; 52846</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30442; 55178</t>
+          <t>30499; 54787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26927; 54345</t>
+          <t>27227; 56812</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26156; 51034</t>
+          <t>26323; 49413</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45373; 75566</t>
+          <t>46543; 74940</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29061; 53893</t>
+          <t>29099; 55090</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38433; 68192</t>
+          <t>38826; 67996</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43480; 72284</t>
+          <t>43619; 73426</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79591; 116940</t>
+          <t>79284; 116662</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64974; 100005</t>
+          <t>64931; 100318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71144; 112483</t>
+          <t>71698; 111919</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19906; 40107</t>
+          <t>20215; 39269</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18332; 37589</t>
+          <t>18910; 37958</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20588; 43031</t>
+          <t>20273; 41384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3639; 26763</t>
+          <t>4278; 33285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49292; 79374</t>
+          <t>48737; 79675</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74204; 112858</t>
+          <t>74304; 111955</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45723; 78447</t>
+          <t>45233; 78582</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>36981; 61586</t>
+          <t>35690; 60217</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>74654; 110725</t>
+          <t>75616; 113256</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96311; 137465</t>
+          <t>98893; 138439</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71360; 112117</t>
+          <t>71816; 109092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44197; 79157</t>
+          <t>45481; 77074</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>211182; 272253</t>
+          <t>213090; 270656</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>254285; 323061</t>
+          <t>254967; 323248</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173441; 228587</t>
+          <t>174026; 228058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151160; 234743</t>
+          <t>157474; 233357</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>151361; 201265</t>
+          <t>151060; 201149</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>228344; 291435</t>
+          <t>226910; 289161</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>164823; 220268</t>
+          <t>164826; 221883</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>169038; 238465</t>
+          <t>167793; 236920</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>380318; 458723</t>
+          <t>377583; 456844</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>502619; 594332</t>
+          <t>502157; 595984</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>351923; 429511</t>
+          <t>353188; 433723</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>348897; 453014</t>
+          <t>349835; 455213</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,83</t>
+          <t>4,98; 10,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,86</t>
+          <t>5,37; 11,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,64</t>
+          <t>3,11; 7,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,77</t>
+          <t>3,16; 6,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,11</t>
+          <t>3,17; 8,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,22</t>
+          <t>3,12; 9,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,95</t>
+          <t>3,68; 8,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,04</t>
+          <t>3,83; 7,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,27</t>
+          <t>4,89; 8,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,23</t>
+          <t>4,87; 9,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,5</t>
+          <t>3,87; 7,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,24</t>
+          <t>3,91; 6,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,37</t>
+          <t>4,71; 10,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,53</t>
+          <t>5,31; 10,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,9</t>
+          <t>2,68; 6,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,31</t>
+          <t>3,55; 8,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,78</t>
+          <t>1,66; 5,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,46</t>
+          <t>5,06; 11,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,45</t>
+          <t>3,59; 8,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,14</t>
+          <t>4,12; 7,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,12</t>
+          <t>3,7; 7,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,11</t>
+          <t>6,01; 10,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,08</t>
+          <t>3,77; 7,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 7,56</t>
+          <t>4,33; 7,31</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,71</t>
+          <t>6,53; 11,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 12,36</t>
+          <t>7,4; 12,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,15</t>
+          <t>4,27; 8,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,74</t>
+          <t>5,68; 10,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,24</t>
+          <t>1,15; 6,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,76</t>
+          <t>3,73; 10,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,79</t>
+          <t>2,73; 10,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,55</t>
+          <t>4,15; 10,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,61</t>
+          <t>5,53; 9,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,73</t>
+          <t>6,69; 10,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,89</t>
+          <t>4,36; 8,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,06</t>
+          <t>5,79; 9,68</t>
         </is>
       </c>
     </row>
@@ -1084,29 +1084,29 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6,55%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,29</t>
+          <t>5,5; 8,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,13</t>
+          <t>6,75; 9,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,53</t>
+          <t>3,96; 6,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,05</t>
+          <t>5,15; 8,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,17</t>
+          <t>4,39; 8,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,48</t>
+          <t>4,82; 8,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,46</t>
+          <t>3,39; 6,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,93</t>
+          <t>5,01; 8,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,72</t>
+          <t>5,5; 7,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,81</t>
+          <t>6,43; 8,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,98</t>
+          <t>4,06; 6,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,06</t>
+          <t>5,59; 8,01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 8,82</t>
+          <t>3,53; 8,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,35</t>
+          <t>5,41; 10,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,83</t>
+          <t>4,9; 9,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 11,96</t>
+          <t>5,13; 10,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,69</t>
+          <t>4,66; 8,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,84</t>
+          <t>5,97; 9,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,46</t>
+          <t>3,94; 7,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,08</t>
+          <t>5,45; 8,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,99</t>
+          <t>4,85; 7,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,17</t>
+          <t>6,34; 9,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,38</t>
+          <t>4,76; 7,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,5</t>
+          <t>5,73; 8,46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,17</t>
+          <t>6,88; 13,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 14,22</t>
+          <t>7,24; 14,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 14,41</t>
+          <t>6,91; 14,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 13,84</t>
+          <t>2,01; 12,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,38</t>
+          <t>3,93; 6,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,09</t>
+          <t>6,62; 9,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,18; 7,26</t>
+          <t>4,22; 7,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,91</t>
+          <t>4,58; 7,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,32</t>
+          <t>4,86; 7,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 10,06</t>
+          <t>6,82; 9,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,97</t>
+          <t>5,28; 8,14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,69</t>
+          <t>4,39; 7,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1557,52 +1557,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,28</t>
+          <t>6,54; 8,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,45</t>
+          <t>7,46; 9,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,74</t>
+          <t>5,12; 6,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,91</t>
+          <t>5,47; 7,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,95</t>
+          <t>4,51; 5,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,15</t>
+          <t>6,32; 8,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 6,28</t>
+          <t>4,71; 6,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,62</t>
+          <t>5,57; 6,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 6,87</t>
+          <t>5,69; 6,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,55</t>
+          <t>7,19; 8,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,55</t>
+          <t>5,68; 6,9</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23796; 46588</t>
+          <t>23576; 47453</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22208; 47494</t>
+          <t>23477; 48562</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13977; 32795</t>
+          <t>13354; 33464</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15308; 34218</t>
+          <t>17376; 37385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9945; 27953</t>
+          <t>9722; 26734</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9595; 28982</t>
+          <t>9796; 28974</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12075; 31052</t>
+          <t>12784; 30438</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16625; 31524</t>
+          <t>18728; 35428</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36958; 64556</t>
+          <t>38165; 64851</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38699; 69358</t>
+          <t>36638; 69052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30462; 58220</t>
+          <t>30005; 55543</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35877; 59482</t>
+          <t>40660; 66350</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50715</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16463; 38035</t>
+          <t>17270; 38388</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22398; 44102</t>
+          <t>22253; 44842</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9524; 26010</t>
+          <t>10111; 26347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15650; 37578</t>
+          <t>17132; 39522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5699; 21507</t>
+          <t>6156; 21603</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17824; 38741</t>
+          <t>17089; 39500</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13976; 35178</t>
+          <t>13354; 32662</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16784; 31157</t>
+          <t>17447; 33473</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26292; 52608</t>
+          <t>27331; 53318</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45856; 76549</t>
+          <t>45505; 76140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26953; 53097</t>
+          <t>28268; 53786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36309; 63142</t>
+          <t>39283; 66223</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33340</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>49959</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36645; 63541</t>
+          <t>35406; 62026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>45351; 77805</t>
+          <t>46559; 78965</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20828; 42550</t>
+          <t>22295; 45344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11800; 58436</t>
+          <t>26772; 49820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1762; 10461</t>
+          <t>1933; 11204</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9239; 25397</t>
+          <t>9696; 27313</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5203; 17919</t>
+          <t>4541; 17552</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7791; 17617</t>
+          <t>7779; 18891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39994; 68250</t>
+          <t>39280; 68736</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60317; 95421</t>
+          <t>59533; 93411</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28773; 54294</t>
+          <t>29964; 55052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19841; 67314</t>
+          <t>38162; 63830</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>55394</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65963; 102641</t>
+          <t>68065; 104460</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79419; 117409</t>
+          <t>78266; 114464</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45342; 75025</t>
+          <t>45534; 74955</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51470; 83262</t>
+          <t>58235; 96774</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31230; 58322</t>
+          <t>31349; 57438</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36470; 65004</t>
+          <t>36932; 63498</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27892; 53319</t>
+          <t>27978; 53912</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25466; 67826</t>
+          <t>43123; 70817</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>106400; 150832</t>
+          <t>107360; 150992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122997; 169692</t>
+          <t>123905; 172352</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80397; 118147</t>
+          <t>80203; 119016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81569; 142206</t>
+          <t>111419; 159665</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>97281</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12942; 30934</t>
+          <t>12389; 30245</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29056; 52846</t>
+          <t>27648; 52516</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30499; 54787</t>
+          <t>30433; 57013</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27227; 56812</t>
+          <t>29156; 59770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26323; 49413</t>
+          <t>26530; 49763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46543; 74940</t>
+          <t>45463; 75341</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29099; 55090</t>
+          <t>29085; 54392</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>38826; 67996</t>
+          <t>45259; 71014</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43619; 73426</t>
+          <t>44629; 73425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79284; 116662</t>
+          <t>80604; 117522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64931; 100318</t>
+          <t>64699; 100744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71698; 111919</t>
+          <t>80104; 118310</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20215; 39269</t>
+          <t>20511; 41297</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18910; 37958</t>
+          <t>19334; 38027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20273; 41384</t>
+          <t>19838; 41493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4278; 33285</t>
+          <t>4762; 29076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>48737; 79675</t>
+          <t>49020; 78984</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74304; 111955</t>
+          <t>73475; 110096</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45233; 78582</t>
+          <t>45708; 77462</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35690; 60217</t>
+          <t>38687; 62783</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>75616; 113256</t>
+          <t>75188; 112698</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98893; 138439</t>
+          <t>93797; 136010</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71816; 109092</t>
+          <t>72272; 111482</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45481; 77074</t>
+          <t>47442; 78940</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197850</t>
+          <t>218192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>405487</t>
+          <t>443604</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>213090; 270656</t>
+          <t>213880; 273587</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>254967; 323248</t>
+          <t>255293; 321932</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174026; 228058</t>
+          <t>173448; 229794</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157474; 233357</t>
+          <t>188370; 255057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>151060; 201149</t>
+          <t>152209; 202362</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>226910; 289161</t>
+          <t>224440; 288992</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>164826; 221883</t>
+          <t>166452; 220950</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>167793; 236920</t>
+          <t>202406; 253637</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>377583; 456844</t>
+          <t>378287; 456746</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>502157; 595984</t>
+          <t>501586; 595727</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>353188; 433723</t>
+          <t>353557; 433584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>349835; 455213</t>
+          <t>402264; 488531</t>
         </is>
       </c>
     </row>
